--- a/data/25Maj-Razorbacks-v-Gold_Diggers.xlsx
+++ b/data/25Maj-Razorbacks-v-Gold_Diggers.xlsx
@@ -244,7 +244,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:O150"/>
   <sheetData>
     <row r="1">
@@ -411,8 +411,10 @@
       <c r="D15" t="s">
         <v>16</v>
       </c>
-      <c r="E15" t="s">
-        <v>17</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -648,8 +650,10 @@
       <c r="D39" t="s">
         <v>19</v>
       </c>
-      <c r="E39" t="s">
-        <v>30</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RGDG</t>
+        </is>
       </c>
       <c r="L39" t="s">
         <v>31</v>
@@ -760,8 +764,10 @@
       <c r="D47" t="s">
         <v>19</v>
       </c>
-      <c r="E47" t="s">
-        <v>41</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
       </c>
       <c r="L47" t="s">
         <v>42</v>
@@ -1106,8 +1112,10 @@
       <c r="D85" t="s">
         <v>16</v>
       </c>
-      <c r="E85" t="s">
-        <v>17</v>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="L85" t="s">
         <v>50</v>
@@ -1320,8 +1328,10 @@
       <c r="D105" t="s">
         <v>59</v>
       </c>
-      <c r="E105" t="s">
-        <v>60</v>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
       </c>
       <c r="F105" t="s">
         <v>18</v>
@@ -1713,8 +1723,10 @@
       <c r="D147" t="s">
         <v>69</v>
       </c>
-      <c r="E147" t="s">
-        <v>70</v>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>DN</t>
+        </is>
       </c>
       <c r="J147" t="s">
         <v>23</v>
